--- a/tams-svreport-parent/tams-svreport/src/main/resources/tpl/EquityBusinessDetails001.xlsx
+++ b/tams-svreport-parent/tams-svreport/src/main/resources/tpl/EquityBusinessDetails001.xlsx
@@ -5,11 +5,11 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\CS\code\XXPL\tams-svreport\src\main\resources\tpl\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\workspace_huaxia\tams\tams-svreport-parent\tams-svreport\src\main\resources\tpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20730" windowHeight="11760"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20736" windowHeight="11760" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="业务明细信息登记" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
     <definedName name="cvb">填写说明!$A$51:$A$87</definedName>
     <definedName name="fgh">填写说明!$A$106:$A$141</definedName>
     <definedName name="gmd">填写说明!$A$7:$A$46</definedName>
-    <definedName name="qd">填写说明!$A$323:$A$329</definedName>
+    <definedName name="qd">填写说明!$A$323:$A$331</definedName>
     <definedName name="qwe">填写说明!$A$106:$A$141</definedName>
     <definedName name="qwqe">填写说明!$A$106:$A$141</definedName>
     <definedName name="rty">填写说明!$A$106:$A$141</definedName>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="359" uniqueCount="323">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="364" uniqueCount="328">
   <si>
     <t>**发行机构代码</t>
   </si>
@@ -141,6 +141,7 @@
         <sz val="12"/>
         <color indexed="8"/>
         <rFont val="等线"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>1.为使导入成功，所有单元格都必须保持模板原有的格式，如须粘贴数据请使用</t>
@@ -1063,12 +1064,70 @@
     <t>**产品代码</t>
     <phoneticPr fontId="10" type="noConversion"/>
   </si>
+  <si>
+    <t>**交易序列号</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>**关联活期存款账号开户行代码</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>**关联活期存款账号开户行名称</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>7</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> 银联交易</t>
+    </r>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>8</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> 第三方支付</t>
+    </r>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="11">
+  <fonts count="12">
     <font>
       <sz val="12"/>
       <name val="宋体"/>
@@ -1078,6 +1137,7 @@
       <sz val="11"/>
       <color indexed="8"/>
       <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
@@ -1092,12 +1152,14 @@
       <sz val="12"/>
       <color indexed="8"/>
       <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="12"/>
       <color indexed="8"/>
       <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
@@ -1137,6 +1199,12 @@
     </font>
     <font>
       <sz val="9"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12"/>
       <name val="宋体"/>
       <family val="3"/>
       <charset val="134"/>
@@ -1278,7 +1346,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1371,6 +1439,9 @@
     </xf>
     <xf numFmtId="49" fontId="7" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1720,30 +1791,33 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AD1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
+  <dimension ref="A1:AG1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.6"/>
   <cols>
-    <col min="1" max="1" width="22.75" style="28" customWidth="1" collapsed="1"/>
+    <col min="1" max="1" width="22.69921875" style="28" customWidth="1" collapsed="1"/>
     <col min="2" max="2" width="18" style="28" customWidth="1" collapsed="1"/>
-    <col min="3" max="14" width="26.125" style="28" customWidth="1" collapsed="1"/>
-    <col min="15" max="16" width="19.375" style="28" customWidth="1" collapsed="1"/>
-    <col min="17" max="18" width="26.125" style="28" customWidth="1" collapsed="1"/>
-    <col min="19" max="19" width="18.5" style="28" customWidth="1" collapsed="1"/>
-    <col min="20" max="20" width="26.125" style="28" customWidth="1" collapsed="1"/>
-    <col min="21" max="21" width="18.375" style="28" customWidth="1" collapsed="1"/>
-    <col min="22" max="22" width="19.375" style="28" customWidth="1" collapsed="1"/>
-    <col min="23" max="23" width="17.5" style="28" customWidth="1" collapsed="1"/>
-    <col min="24" max="24" width="24" style="28" customWidth="1" collapsed="1"/>
-    <col min="25" max="25" width="15.5" style="28" customWidth="1" collapsed="1"/>
-    <col min="26" max="26" width="16.875" style="28" customWidth="1" collapsed="1"/>
-    <col min="27" max="27" width="17.375" style="28" customWidth="1" collapsed="1"/>
-    <col min="28" max="28" width="9" style="29" collapsed="1"/>
-    <col min="29" max="29" width="9" style="29"/>
-    <col min="30" max="30" width="0" style="29" hidden="1" customWidth="1"/>
-    <col min="31" max="16384" width="9" style="29" collapsed="1"/>
+    <col min="3" max="9" width="26.09765625" style="28" customWidth="1" collapsed="1"/>
+    <col min="10" max="10" width="30.09765625" style="28" customWidth="1" collapsed="1"/>
+    <col min="11" max="11" width="30.59765625" style="28" customWidth="1" collapsed="1"/>
+    <col min="12" max="17" width="26.09765625" style="28" customWidth="1" collapsed="1"/>
+    <col min="18" max="19" width="19.3984375" style="28" customWidth="1" collapsed="1"/>
+    <col min="20" max="21" width="26.09765625" style="28" customWidth="1" collapsed="1"/>
+    <col min="22" max="22" width="18.5" style="28" customWidth="1" collapsed="1"/>
+    <col min="23" max="23" width="26.09765625" style="28" customWidth="1" collapsed="1"/>
+    <col min="24" max="24" width="18.3984375" style="28" customWidth="1" collapsed="1"/>
+    <col min="25" max="25" width="19.3984375" style="28" customWidth="1" collapsed="1"/>
+    <col min="26" max="26" width="17.5" style="28" customWidth="1" collapsed="1"/>
+    <col min="27" max="27" width="24" style="28" customWidth="1" collapsed="1"/>
+    <col min="28" max="28" width="15.5" style="28" customWidth="1" collapsed="1"/>
+    <col min="29" max="29" width="16.8984375" style="28" customWidth="1" collapsed="1"/>
+    <col min="30" max="30" width="17.3984375" style="28" customWidth="1" collapsed="1"/>
+    <col min="31" max="31" width="9" style="29" collapsed="1"/>
+    <col min="32" max="32" width="9" style="29"/>
+    <col min="33" max="33" width="0" style="29" hidden="1" customWidth="1"/>
+    <col min="34" max="16384" width="9" style="29" collapsed="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27">
+    <row r="1" spans="1:30">
       <c r="A1" s="30" t="s">
         <v>0</v>
       </c>
@@ -1766,92 +1840,101 @@
         <v>6</v>
       </c>
       <c r="H1" s="30" t="s">
+        <v>323</v>
+      </c>
+      <c r="I1" s="30" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="30" t="s">
+      <c r="J1" s="30" t="s">
+        <v>324</v>
+      </c>
+      <c r="K1" s="30" t="s">
+        <v>325</v>
+      </c>
+      <c r="L1" s="30" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="30" t="s">
+      <c r="M1" s="30" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="30" t="s">
+      <c r="N1" s="30" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="30" t="s">
+      <c r="O1" s="30" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="30" t="s">
+      <c r="P1" s="30" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="30" t="s">
+      <c r="Q1" s="30" t="s">
         <v>322</v>
       </c>
-      <c r="O1" s="30" t="s">
+      <c r="R1" s="30" t="s">
         <v>13</v>
       </c>
-      <c r="P1" s="30" t="s">
+      <c r="S1" s="30" t="s">
         <v>14</v>
       </c>
-      <c r="Q1" s="30" t="s">
+      <c r="T1" s="30" t="s">
         <v>15</v>
       </c>
-      <c r="R1" s="30" t="s">
+      <c r="U1" s="30" t="s">
         <v>16</v>
       </c>
-      <c r="S1" s="30" t="s">
+      <c r="V1" s="30" t="s">
         <v>17</v>
       </c>
-      <c r="T1" s="30" t="s">
+      <c r="W1" s="30" t="s">
         <v>18</v>
       </c>
-      <c r="U1" s="30" t="s">
+      <c r="X1" s="30" t="s">
         <v>19</v>
       </c>
-      <c r="V1" s="30" t="s">
+      <c r="Y1" s="30" t="s">
         <v>20</v>
       </c>
-      <c r="W1" s="30" t="s">
+      <c r="Z1" s="30" t="s">
         <v>21</v>
       </c>
-      <c r="X1" s="30" t="s">
+      <c r="AA1" s="30" t="s">
         <v>22</v>
       </c>
-      <c r="Y1" s="30" t="s">
+      <c r="AB1" s="30" t="s">
         <v>23</v>
       </c>
-      <c r="Z1" s="30" t="s">
+      <c r="AC1" s="30" t="s">
         <v>24</v>
       </c>
-      <c r="AA1" s="30" t="s">
+      <c r="AD1" s="30" t="s">
         <v>25</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="10" type="noConversion"/>
   <dataValidations count="9">
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Y1 S1 O1"/>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Q4">
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AB1 V1 R1"/>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="T4">
       <formula1>qwe</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S2:S1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="V2:V1048576">
       <formula1>bz</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O2:O1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R2:R1048576">
       <formula1>ywzl</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Y2:Y1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AB2:AB1048576">
       <formula1>qd</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I2:I1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L2:L1048576">
       <formula1>asd</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J2:J1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M2:M1048576">
       <formula1>zxc</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M2:M1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P2:P1048576">
       <formula1>cvb</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P2 P3:P1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S2:S1048576">
       <formula1>fgh</formula1>
     </dataValidation>
   </dataValidations>
@@ -1862,36 +1945,36 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:A329"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
+  <dimension ref="A1:A331"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.6"/>
   <cols>
-    <col min="1" max="1" width="73.375" customWidth="1" collapsed="1"/>
+    <col min="1" max="1" width="73.3984375" customWidth="1" collapsed="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="15.75">
+    <row r="1" spans="1:1">
       <c r="A1" s="6" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="2" spans="1:1" ht="30">
+    <row r="2" spans="1:1" ht="31.8">
       <c r="A2" s="7" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="3" spans="1:1" ht="15.75">
+    <row r="3" spans="1:1">
       <c r="A3" s="8" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="4" spans="1:1" ht="15.75">
+    <row r="4" spans="1:1">
       <c r="A4" s="9" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="5" spans="1:1" ht="15.75">
+    <row r="5" spans="1:1">
       <c r="A5" s="10"/>
     </row>
-    <row r="6" spans="1:1" ht="15.75">
+    <row r="6" spans="1:1">
       <c r="A6" s="11" t="s">
         <v>36</v>
       </c>
@@ -3502,7 +3585,17 @@
       </c>
     </row>
     <row r="329" spans="1:1">
-      <c r="A329" s="27" t="s">
+      <c r="A329" s="31" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="330" spans="1:1">
+      <c r="A330" s="31" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="331" spans="1:1">
+      <c r="A331" s="27" t="s">
         <v>316</v>
       </c>
     </row>
@@ -3516,9 +3609,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.6"/>
   <cols>
-    <col min="1" max="1" width="14.625" customWidth="1" collapsed="1"/>
+    <col min="1" max="1" width="14.59765625" customWidth="1" collapsed="1"/>
     <col min="2" max="2" width="34" customWidth="1" collapsed="1"/>
   </cols>
   <sheetData>
